--- a/基础化工.xlsx
+++ b/基础化工.xlsx
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I2992"/>
+  <dimension ref="B2:I2993"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="14.19921875" customWidth="1" style="1" min="2" max="2"/>
@@ -49947,6 +49947,20 @@
       </c>
       <c r="E2992" t="n">
         <v>1426</v>
+      </c>
+    </row>
+    <row r="2993">
+      <c r="B2993" s="25" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C2993" t="n">
+        <v>5223</v>
+      </c>
+      <c r="D2993" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E2993" t="n">
+        <v>1441</v>
       </c>
     </row>
   </sheetData>
@@ -68314,7 +68328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E1026"/>
+  <dimension ref="B2:E1027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="17.06640625" customWidth="1" style="6" min="2" max="2"/>
@@ -82519,6 +82533,14 @@
         <v>0.884</v>
       </c>
     </row>
+    <row r="1027">
+      <c r="B1027" s="25" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C1027" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -82530,7 +82552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F538"/>
+  <dimension ref="B2:F539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="11.1328125" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
@@ -91697,6 +91719,23 @@
         <v>3132</v>
       </c>
     </row>
+    <row r="539">
+      <c r="B539" s="25" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C539" t="n">
+        <v>17</v>
+      </c>
+      <c r="D539" t="n">
+        <v>1595</v>
+      </c>
+      <c r="E539" t="n">
+        <v>1840</v>
+      </c>
+      <c r="F539" t="n">
+        <v>2985</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/基础化工.xlsx
+++ b/基础化工.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\报告\000临时工作\20250927平安资管周度更新\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60311CC7-24B2-43AA-83FA-EEF5B8FADE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1473FD-94A0-44A5-BC6E-937093442735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -163,7 +163,7 @@
     <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="186" formatCode="yyyy\-mm\-dd_ "/>
+    <numFmt numFmtId="182" formatCode="yyyy\-mm\-dd_ "/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -253,7 +253,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -321,11 +321,14 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -22000,7 +22003,7 @@
         <v>91.72</v>
       </c>
     </row>
-    <row r="993" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="993" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B993" s="3">
         <v>43353</v>
       </c>
@@ -22019,8 +22022,11 @@
       <c r="H993" s="6">
         <v>10400</v>
       </c>
-    </row>
-    <row r="994" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I993" s="6">
+        <v>98.6</v>
+      </c>
+    </row>
+    <row r="994" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B994" s="3">
         <v>43354</v>
       </c>
@@ -22033,8 +22039,17 @@
       <c r="E994" s="4">
         <v>2020</v>
       </c>
-    </row>
-    <row r="995" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G994" s="8">
+        <v>46131</v>
+      </c>
+      <c r="H994" s="6">
+        <v>10270</v>
+      </c>
+      <c r="I994" s="6">
+        <v>103.71</v>
+      </c>
+    </row>
+    <row r="995" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B995" s="3">
         <v>43355</v>
       </c>
@@ -22048,7 +22063,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="996" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="996" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B996" s="3">
         <v>43356</v>
       </c>
@@ -22062,7 +22077,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="997" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="997" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B997" s="3">
         <v>43357</v>
       </c>
@@ -22076,7 +22091,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="998" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="998" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B998" s="3">
         <v>43360</v>
       </c>
@@ -22090,7 +22105,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="999" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="999" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B999" s="3">
         <v>43361</v>
       </c>
@@ -22104,7 +22119,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="1000" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1000" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1000" s="3">
         <v>43362</v>
       </c>
@@ -22118,7 +22133,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="1001" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1001" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1001" s="3">
         <v>43363</v>
       </c>
@@ -22132,7 +22147,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="1002" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1002" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1002" s="3">
         <v>43364</v>
       </c>
@@ -22146,7 +22161,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="1003" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1003" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1003" s="3">
         <v>43367</v>
       </c>
@@ -22160,7 +22175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1004" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1004" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1004" s="3">
         <v>43368</v>
       </c>
@@ -22174,7 +22189,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="1005" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1005" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1005" s="3">
         <v>43369</v>
       </c>
@@ -22188,7 +22203,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="1006" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1006" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1006" s="3">
         <v>43370</v>
       </c>
@@ -22202,7 +22217,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="1007" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1007" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1007" s="3">
         <v>43371</v>
       </c>
@@ -22216,7 +22231,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="1008" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1008" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1008" s="3">
         <v>43372</v>
       </c>
@@ -68352,7 +68367,9 @@
       <c r="C904" s="12">
         <v>42.5</v>
       </c>
-      <c r="D904" s="12"/>
+      <c r="D904" s="21">
+        <v>5.5</v>
+      </c>
       <c r="E904" s="12">
         <v>28.5</v>
       </c>
@@ -68364,12 +68381,22 @@
       </c>
     </row>
     <row r="905" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B905" s="11"/>
+      <c r="B905" s="11">
+        <v>46135</v>
+      </c>
       <c r="C905" s="12"/>
-      <c r="D905" s="12"/>
-      <c r="E905" s="12"/>
-      <c r="F905" s="12"/>
-      <c r="G905" s="12"/>
+      <c r="D905" s="21">
+        <v>5.49</v>
+      </c>
+      <c r="E905" s="25">
+        <v>28.9</v>
+      </c>
+      <c r="F905" s="25">
+        <v>32.5</v>
+      </c>
+      <c r="G905" s="25">
+        <v>34.200000000000003</v>
+      </c>
     </row>
     <row r="906" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B906" s="11"/>
@@ -68667,7 +68694,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{864CCCF4-8B1B-4DE0-ACFE-3FC4EDAB7634}">
-  <dimension ref="B2:E1029"/>
+  <dimension ref="B2:E1030"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.08203125" style="6" customWidth="1"/>
@@ -82904,6 +82931,14 @@
         <v>0.5272</v>
       </c>
     </row>
+    <row r="1030" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B1030" s="11">
+        <v>46135</v>
+      </c>
+      <c r="D1030" s="21">
+        <v>82.71</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -82912,7 +82947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99632C68-07D6-4E3F-8F51-79061A4109F0}">
-  <dimension ref="B2:F542"/>
+  <dimension ref="B2:F543"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.1640625" style="6" bestFit="1" customWidth="1"/>
@@ -92105,7 +92140,7 @@
         <v>46130</v>
       </c>
       <c r="C542" s="18">
-        <v>38.752500000000055</v>
+        <v>55</v>
       </c>
       <c r="D542" s="16">
         <v>1862.0790000000002</v>
@@ -92115,6 +92150,23 @@
       </c>
       <c r="F542" s="16">
         <v>3077.0790000000002</v>
+      </c>
+    </row>
+    <row r="543" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B543" s="17">
+        <v>46137</v>
+      </c>
+      <c r="C543" s="6">
+        <v>150</v>
+      </c>
+      <c r="D543" s="6">
+        <v>1565.1490000000001</v>
+      </c>
+      <c r="E543" s="6">
+        <v>1965.1490000000001</v>
+      </c>
+      <c r="F543" s="6">
+        <v>2715.1490000000003</v>
       </c>
     </row>
   </sheetData>

--- a/基础化工.xlsx
+++ b/基础化工.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\报告\000临时工作\20250927平安资管周度更新\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1473FD-94A0-44A5-BC6E-937093442735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166168F2-711A-4D2B-896F-363EB8C10E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
   <si>
     <t>指标名称</t>
   </si>
@@ -99,15 +99,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>中国:华东港口:库存量:甲醇</t>
-  </si>
-  <si>
-    <t>中国:开工率:尿素</t>
-  </si>
-  <si>
-    <t>中国:江浙地区:开工率:涤纶长丝</t>
-  </si>
-  <si>
     <t>涤纶长丝(POY)-PTA-MEG价差</t>
   </si>
   <si>
@@ -151,6 +142,22 @@
     <t>中国化工产品价格指数</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>中国:华东港口:库存量:甲醇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国:开工率:尿素</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国:江浙地区:开工率:涤纶长丝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>90,17%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -165,7 +172,7 @@
     <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="182" formatCode="yyyy\-mm\-dd_ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,13 +235,24 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -253,7 +271,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -329,6 +347,9 @@
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -612,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:I3012"/>
+  <dimension ref="B2:I3027"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.1640625" style="1" customWidth="1"/>
@@ -629,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>1</v>
@@ -675,7 +696,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -22062,6 +22083,15 @@
       <c r="E995" s="4">
         <v>2035</v>
       </c>
+      <c r="G995" s="8">
+        <v>46138</v>
+      </c>
+      <c r="H995" s="24">
+        <v>9940</v>
+      </c>
+      <c r="I995" s="24">
+        <v>99.45</v>
+      </c>
     </row>
     <row r="996" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B996" s="3">
@@ -22076,6 +22106,13 @@
       <c r="E996" s="4">
         <v>2050</v>
       </c>
+      <c r="G996" s="8">
+        <v>46145</v>
+      </c>
+      <c r="H996" s="24">
+        <v>9812.5</v>
+      </c>
+      <c r="I996" s="24"/>
     </row>
     <row r="997" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B997" s="3">
@@ -50298,6 +50335,206 @@
         <v>1401</v>
       </c>
       <c r="E3012" s="24">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="3013" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3013" s="23">
+        <v>46132</v>
+      </c>
+      <c r="C3013" s="24">
+        <v>5261</v>
+      </c>
+      <c r="D3013" s="24">
+        <v>1371</v>
+      </c>
+      <c r="E3013" s="24">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="3014" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3014" s="23">
+        <v>46133</v>
+      </c>
+      <c r="C3014" s="24">
+        <v>5227</v>
+      </c>
+      <c r="D3014" s="24">
+        <v>1371</v>
+      </c>
+      <c r="E3014" s="24">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="3015" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3015" s="23">
+        <v>46134</v>
+      </c>
+      <c r="C3015" s="24">
+        <v>5203</v>
+      </c>
+      <c r="D3015" s="24">
+        <v>1381</v>
+      </c>
+      <c r="E3015" s="24">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="3016" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3016" s="23">
+        <v>46135</v>
+      </c>
+      <c r="C3016" s="24">
+        <v>5213</v>
+      </c>
+      <c r="D3016" s="24">
+        <v>1381</v>
+      </c>
+      <c r="E3016" s="24">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="3017" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3017" s="23">
+        <v>46136</v>
+      </c>
+      <c r="C3017" s="24">
+        <v>5212</v>
+      </c>
+      <c r="D3017" s="24">
+        <v>1381</v>
+      </c>
+      <c r="E3017" s="24">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="3018" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3018" s="23">
+        <v>46139</v>
+      </c>
+      <c r="C3018" s="24">
+        <v>5218</v>
+      </c>
+      <c r="D3018" s="24">
+        <v>1361</v>
+      </c>
+      <c r="E3018" s="24">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="3019" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3019" s="23">
+        <v>46140</v>
+      </c>
+      <c r="C3019" s="24">
+        <v>5268</v>
+      </c>
+      <c r="D3019" s="24">
+        <v>1351</v>
+      </c>
+      <c r="E3019" s="24">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="3020" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3020" s="23">
+        <v>46141</v>
+      </c>
+      <c r="C3020" s="24">
+        <v>5299</v>
+      </c>
+      <c r="D3020" s="24">
+        <v>1321</v>
+      </c>
+      <c r="E3020" s="24">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="3021" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3021" s="23">
+        <v>46142</v>
+      </c>
+      <c r="C3021" s="24">
+        <v>5317</v>
+      </c>
+      <c r="D3021" s="24">
+        <v>1321</v>
+      </c>
+      <c r="E3021" s="24">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="3022" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3022" s="23">
+        <v>46146</v>
+      </c>
+      <c r="C3022" s="24"/>
+      <c r="D3022" s="24">
+        <v>1281</v>
+      </c>
+      <c r="E3022" s="24"/>
+    </row>
+    <row r="3023" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3023" s="23">
+        <v>46147</v>
+      </c>
+      <c r="C3023" s="24"/>
+      <c r="D3023" s="24">
+        <v>1281</v>
+      </c>
+      <c r="E3023" s="24"/>
+    </row>
+    <row r="3024" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3024" s="23">
+        <v>46148</v>
+      </c>
+      <c r="C3024" s="24">
+        <v>5344</v>
+      </c>
+      <c r="D3024" s="24">
+        <v>1281</v>
+      </c>
+      <c r="E3024" s="24">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="3025" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3025" s="23">
+        <v>46149</v>
+      </c>
+      <c r="C3025" s="24">
+        <v>5296</v>
+      </c>
+      <c r="D3025" s="24">
+        <v>1251</v>
+      </c>
+      <c r="E3025" s="24">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="3026" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3026" s="23">
+        <v>46150</v>
+      </c>
+      <c r="C3026" s="24">
+        <v>5219</v>
+      </c>
+      <c r="D3026" s="24">
+        <v>1211</v>
+      </c>
+      <c r="E3026" s="24">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="3027" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3027" s="23">
+        <v>46151</v>
+      </c>
+      <c r="C3027" s="24">
+        <v>5201</v>
+      </c>
+      <c r="D3027" s="24"/>
+      <c r="E3027" s="24">
         <v>1890</v>
       </c>
     </row>
@@ -50325,7 +50562,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>14</v>
@@ -68384,7 +68621,9 @@
       <c r="B905" s="11">
         <v>46135</v>
       </c>
-      <c r="C905" s="12"/>
+      <c r="C905" s="12">
+        <v>43.11</v>
+      </c>
       <c r="D905" s="21">
         <v>5.49</v>
       </c>
@@ -68399,20 +68638,44 @@
       </c>
     </row>
     <row r="906" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B906" s="11"/>
-      <c r="C906" s="12"/>
-      <c r="D906" s="12"/>
-      <c r="E906" s="12"/>
-      <c r="F906" s="12"/>
-      <c r="G906" s="12"/>
+      <c r="B906" s="11">
+        <v>46142</v>
+      </c>
+      <c r="C906" s="24">
+        <v>43.94</v>
+      </c>
+      <c r="D906" s="24">
+        <v>5.19</v>
+      </c>
+      <c r="E906" s="24">
+        <v>22.9</v>
+      </c>
+      <c r="F906" s="24">
+        <v>33.4</v>
+      </c>
+      <c r="G906" s="24">
+        <v>30.2</v>
+      </c>
     </row>
     <row r="907" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B907" s="11"/>
-      <c r="C907" s="12"/>
-      <c r="D907" s="12"/>
-      <c r="E907" s="12"/>
-      <c r="F907" s="12"/>
-      <c r="G907" s="12"/>
+      <c r="B907" s="11">
+        <v>46149</v>
+      </c>
+      <c r="C907" s="24">
+        <v>52.12</v>
+      </c>
+      <c r="D907" s="24">
+        <v>5.01</v>
+      </c>
+      <c r="E907" s="24">
+        <v>27.5</v>
+      </c>
+      <c r="F907" s="24">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="G907" s="24">
+        <v>33.200000000000003</v>
+      </c>
     </row>
     <row r="908" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B908" s="11"/>
@@ -68694,7 +68957,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{864CCCF4-8B1B-4DE0-ACFE-3FC4EDAB7634}">
-  <dimension ref="B2:E1030"/>
+  <dimension ref="B2:E1032"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.08203125" style="6" customWidth="1"/>
@@ -68708,13 +68971,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
@@ -82882,10 +83145,10 @@
       <c r="C1026" s="22">
         <v>0.88349999999999995</v>
       </c>
-      <c r="D1026" s="21">
+      <c r="D1026" s="14">
         <v>0.87490000000000001</v>
       </c>
-      <c r="E1026" s="22">
+      <c r="E1026" s="14">
         <v>0.53559999999999997</v>
       </c>
     </row>
@@ -82896,10 +83159,10 @@
       <c r="C1027" s="22">
         <v>0.91910000000000003</v>
       </c>
-      <c r="D1027" s="21">
+      <c r="D1027" s="14">
         <v>0.86729999999999996</v>
       </c>
-      <c r="E1027" s="22">
+      <c r="E1027" s="14">
         <v>0.5353</v>
       </c>
     </row>
@@ -82910,10 +83173,10 @@
       <c r="C1028" s="22">
         <v>0.92600000000000005</v>
       </c>
-      <c r="D1028" s="21">
+      <c r="D1028" s="14">
         <v>0.85170000000000001</v>
       </c>
-      <c r="E1028" s="22">
+      <c r="E1028" s="14">
         <v>0.53139999999999998</v>
       </c>
     </row>
@@ -82924,10 +83187,10 @@
       <c r="C1029" s="22">
         <v>0.90310000000000001</v>
       </c>
-      <c r="D1029" s="21">
+      <c r="D1029" s="14">
         <v>0.85060000000000002</v>
       </c>
-      <c r="E1029" s="22">
+      <c r="E1029" s="14">
         <v>0.5272</v>
       </c>
     </row>
@@ -82935,8 +83198,42 @@
       <c r="B1030" s="11">
         <v>46135</v>
       </c>
-      <c r="D1030" s="21">
-        <v>82.71</v>
+      <c r="C1030" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1030" s="14">
+        <v>0.82709999999999995</v>
+      </c>
+      <c r="E1030" s="14">
+        <v>0.51829999999999998</v>
+      </c>
+    </row>
+    <row r="1031" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B1031" s="11">
+        <v>46142</v>
+      </c>
+      <c r="C1031" s="22">
+        <v>0.92010000000000003</v>
+      </c>
+      <c r="D1031" s="14">
+        <v>0.81879999999999997</v>
+      </c>
+      <c r="E1031" s="14">
+        <v>0.49990000000000001</v>
+      </c>
+    </row>
+    <row r="1032" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B1032" s="11">
+        <v>46149</v>
+      </c>
+      <c r="C1032" s="6">
+        <v>94.44</v>
+      </c>
+      <c r="D1032" s="14">
+        <v>0.82379999999999998</v>
+      </c>
+      <c r="E1032" s="14">
+        <v>0.51819999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -82947,7 +83244,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99632C68-07D6-4E3F-8F51-79061A4109F0}">
-  <dimension ref="B2:F543"/>
+  <dimension ref="B2:F545"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.1640625" style="6" bestFit="1" customWidth="1"/>
@@ -82959,19 +83256,19 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>29</v>
-      </c>
       <c r="D2" s="13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
@@ -82979,7 +83276,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>10</v>
@@ -82993,19 +83290,19 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
@@ -92157,7 +92454,7 @@
         <v>46137</v>
       </c>
       <c r="C543" s="6">
-        <v>150</v>
+        <v>136.18000000000006</v>
       </c>
       <c r="D543" s="6">
         <v>1565.1490000000001</v>
@@ -92165,8 +92462,42 @@
       <c r="E543" s="6">
         <v>1965.1490000000001</v>
       </c>
-      <c r="F543" s="6">
+      <c r="F543" s="26">
         <v>2715.1490000000003</v>
+      </c>
+    </row>
+    <row r="544" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B544" s="17">
+        <v>46144</v>
+      </c>
+      <c r="C544" s="6">
+        <v>100.35500000000002</v>
+      </c>
+      <c r="D544" s="6">
+        <v>1041.3300000000002</v>
+      </c>
+      <c r="E544" s="6">
+        <v>1472.5800000000002</v>
+      </c>
+      <c r="F544" s="26">
+        <v>2253.83</v>
+      </c>
+    </row>
+    <row r="545" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B545" s="17">
+        <v>46151</v>
+      </c>
+      <c r="C545" s="6">
+        <v>194.92399999999998</v>
+      </c>
+      <c r="D545" s="6">
+        <v>1312.3174999999997</v>
+      </c>
+      <c r="E545" s="6">
+        <v>1662.3174999999997</v>
+      </c>
+      <c r="F545" s="26">
+        <v>2362.3174999999997</v>
       </c>
     </row>
   </sheetData>
